--- a/artfynd/A 26645-2026 artfynd.xlsx
+++ b/artfynd/A 26645-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113441438</v>
+        <v>113441401</v>
       </c>
       <c r="B2" t="n">
-        <v>91628</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5966</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>786219</v>
+        <v>785979</v>
       </c>
       <c r="R2" t="n">
-        <v>7217228</v>
+        <v>7216888</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,15 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113441439</v>
+        <v>113441518</v>
       </c>
       <c r="B3" t="n">
-        <v>91628</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,21 +788,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>785964</v>
+        <v>786155</v>
       </c>
       <c r="R3" t="n">
-        <v>7216907</v>
+        <v>7217076</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,15 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113441460</v>
+        <v>113441523</v>
       </c>
       <c r="B4" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -905,21 +890,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>786139</v>
+        <v>786175</v>
       </c>
       <c r="R4" t="n">
-        <v>7217057</v>
+        <v>7217437</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,37 +981,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113441518</v>
+        <v>113441419</v>
       </c>
       <c r="B5" t="n">
-        <v>91605</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>786155</v>
+        <v>785912</v>
       </c>
       <c r="R5" t="n">
-        <v>7217076</v>
+        <v>7216875</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1103,37 +1083,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113441420</v>
+        <v>113441438</v>
       </c>
       <c r="B6" t="n">
-        <v>91617</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4366</v>
+        <v>5966</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1143,10 +1118,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>785912</v>
+        <v>786219</v>
       </c>
       <c r="R6" t="n">
-        <v>7216875</v>
+        <v>7217228</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1210,15 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113441401</v>
+        <v>113441439</v>
       </c>
       <c r="B7" t="n">
-        <v>90332</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1226,21 +1196,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>5966</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1250,10 +1220,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>785979</v>
+        <v>785964</v>
       </c>
       <c r="R7" t="n">
-        <v>7216888</v>
+        <v>7216907</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1317,37 +1287,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113441448</v>
+        <v>113441460</v>
       </c>
       <c r="B8" t="n">
-        <v>78246</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1357,10 +1322,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>785935</v>
+        <v>786139</v>
       </c>
       <c r="R8" t="n">
-        <v>7216929</v>
+        <v>7217057</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1424,37 +1389,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113441523</v>
+        <v>113441461</v>
       </c>
       <c r="B9" t="n">
-        <v>91605</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1464,10 +1424,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>786175</v>
+        <v>786080</v>
       </c>
       <c r="R9" t="n">
-        <v>7217437</v>
+        <v>7216837</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1528,6 +1488,108 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>113441448</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79084</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Västerbottens län, Vb</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>785935</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7216929</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Byske</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2023-09-06</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2023-09-06</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Sweco NVI</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Tobias Pettersson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Tobias Pettersson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 26645-2026 artfynd.xlsx
+++ b/artfynd/A 26645-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113441518</v>
+        <v>134650454</v>
       </c>
       <c r="B3" t="n">
-        <v>93197</v>
+        <v>91974</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,34 +788,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Västerbottens län, Vb</t>
+          <t>Nördrengårdsmyran, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>786155</v>
+        <v>785960</v>
       </c>
       <c r="R3" t="n">
-        <v>7217076</v>
+        <v>7216878</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -842,17 +842,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-09-06</t>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-09-06</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Sweco NVI</t>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -867,22 +872,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Tobias Pettersson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Tobias Pettersson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113441523</v>
+        <v>134650456</v>
       </c>
       <c r="B4" t="n">
-        <v>93197</v>
+        <v>91974</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -890,34 +895,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Västerbottens län, Vb</t>
+          <t>Nördrengårdsmyran, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>786175</v>
+        <v>786000</v>
       </c>
       <c r="R4" t="n">
-        <v>7217437</v>
+        <v>7216891</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -944,17 +949,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-09-06</t>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-09-06</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Sweco NVI</t>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -969,22 +979,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Tobias Pettersson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Tobias Pettersson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113441419</v>
+        <v>113441518</v>
       </c>
       <c r="B5" t="n">
-        <v>93209</v>
+        <v>93197</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -992,21 +1002,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1016,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>785912</v>
+        <v>786155</v>
       </c>
       <c r="R5" t="n">
-        <v>7216875</v>
+        <v>7217076</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113441438</v>
+        <v>113441523</v>
       </c>
       <c r="B6" t="n">
-        <v>93235</v>
+        <v>93197</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1094,21 +1104,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1118,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>786219</v>
+        <v>786175</v>
       </c>
       <c r="R6" t="n">
-        <v>7217228</v>
+        <v>7217437</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113441439</v>
+        <v>134650458</v>
       </c>
       <c r="B7" t="n">
-        <v>93235</v>
+        <v>93271</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1196,34 +1206,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Västerbottens län, Vb</t>
+          <t>Nördrengårdsmyran, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>785964</v>
+        <v>785985</v>
       </c>
       <c r="R7" t="n">
-        <v>7216907</v>
+        <v>7216828</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1250,17 +1260,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-09-06</t>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-09-06</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Sweco NVI</t>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1275,44 +1290,44 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Tobias Pettersson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Tobias Pettersson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113441460</v>
+        <v>113441419</v>
       </c>
       <c r="B8" t="n">
-        <v>79327</v>
+        <v>93209</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>4366</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1322,10 +1337,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>786139</v>
+        <v>785912</v>
       </c>
       <c r="R8" t="n">
-        <v>7217057</v>
+        <v>7216875</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,32 +1404,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113441461</v>
+        <v>113441438</v>
       </c>
       <c r="B9" t="n">
-        <v>79327</v>
+        <v>93235</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>5966</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1424,10 +1439,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>786080</v>
+        <v>786219</v>
       </c>
       <c r="R9" t="n">
-        <v>7216837</v>
+        <v>7217228</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1506,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113441448</v>
+        <v>113441439</v>
       </c>
       <c r="B10" t="n">
-        <v>79084</v>
+        <v>93235</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1502,21 +1517,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6446</v>
+        <v>5966</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1526,10 +1541,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>785935</v>
+        <v>785964</v>
       </c>
       <c r="R10" t="n">
-        <v>7216929</v>
+        <v>7216907</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1590,6 +1605,766 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>113441460</v>
+      </c>
+      <c r="B11" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Västerbottens län, Vb</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>786139</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7217057</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Byske</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2023-09-06</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2023-09-06</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Sweco NVI</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Tobias Pettersson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Tobias Pettersson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>113441461</v>
+      </c>
+      <c r="B12" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Västerbottens län, Vb</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>786080</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7216837</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Byske</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2023-09-06</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2023-09-06</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Sweco NVI</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Tobias Pettersson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Tobias Pettersson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>134650489</v>
+      </c>
+      <c r="B13" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Nördrengårdsmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>786100</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7217086</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Byske</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>12:58</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>12:58</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>113441448</v>
+      </c>
+      <c r="B14" t="n">
+        <v>79084</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Västerbottens län, Vb</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>785935</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7216929</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Byske</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2023-09-06</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2023-09-06</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Sweco NVI</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Tobias Pettersson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Tobias Pettersson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>134650462</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Nördrengårdsmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>786092</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7216833</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Byske</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>11:52</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>11:52</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Barksprätt</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>134650464</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Nördrengårdsmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>786099</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7216832</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Byske</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Färska barksprätt bild</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>134650460</v>
+      </c>
+      <c r="B17" t="n">
+        <v>99217</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Nördrengårdsmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>786013</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7216864</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Byske</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 26645-2026 artfynd.xlsx
+++ b/artfynd/A 26645-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AZ17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113441401</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -881,6 +891,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134650454</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -988,6 +1003,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134650456</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1090,6 +1110,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113441518</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1192,6 +1217,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113441523</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1299,6 +1329,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134650458</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1401,6 +1436,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113441419</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1503,6 +1543,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113441438</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1605,6 +1650,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113441439</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1707,6 +1757,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113441460</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1809,6 +1864,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113441461</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1916,6 +1976,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134650489</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2018,6 +2083,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113441448</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2138,6 +2208,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134650462</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2258,6 +2333,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134650464</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2365,8 +2445,31 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134650460</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 26645-2026 artfynd.xlsx
+++ b/artfynd/A 26645-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ10"/>
+  <dimension ref="A1:AZ17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113441518</v>
+        <v>134650454</v>
       </c>
       <c r="B3" t="n">
-        <v>93197</v>
+        <v>92048</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,34 +798,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Västerbottens län, Vb</t>
+          <t>Nördrengårdsmyran, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>786155</v>
+        <v>785960</v>
       </c>
       <c r="R3" t="n">
-        <v>7217076</v>
+        <v>7216878</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,17 +852,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-09-06</t>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-09-06</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Sweco NVI</t>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -877,27 +882,31 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Tobias Pettersson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Tobias Pettersson</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/113441518</t>
+          <t>https://artportalen.se/Sighting/134650454</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113441523</v>
+        <v>134650456</v>
       </c>
       <c r="B4" t="n">
-        <v>93197</v>
+        <v>92048</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -905,34 +914,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Västerbottens län, Vb</t>
+          <t>Nördrengårdsmyran, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>786175</v>
+        <v>786000</v>
       </c>
       <c r="R4" t="n">
-        <v>7217437</v>
+        <v>7216891</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,17 +968,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-09-06</t>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-09-06</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Sweco NVI</t>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -984,27 +998,31 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Tobias Pettersson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Tobias Pettersson</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/113441523</t>
+          <t>https://artportalen.se/Sighting/134650456</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113441419</v>
+        <v>113441518</v>
       </c>
       <c r="B5" t="n">
-        <v>93209</v>
+        <v>93197</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1012,21 +1030,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1054,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>785912</v>
+        <v>786155</v>
       </c>
       <c r="R5" t="n">
-        <v>7216875</v>
+        <v>7217076</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1102,16 +1120,16 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/113441419</t>
+          <t>https://artportalen.se/Sighting/113441518</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113441438</v>
+        <v>113441523</v>
       </c>
       <c r="B6" t="n">
-        <v>93235</v>
+        <v>93197</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1119,21 +1137,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1143,10 +1161,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>786219</v>
+        <v>786175</v>
       </c>
       <c r="R6" t="n">
-        <v>7217228</v>
+        <v>7217437</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1209,16 +1227,16 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/113441438</t>
+          <t>https://artportalen.se/Sighting/113441523</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113441439</v>
+        <v>134650458</v>
       </c>
       <c r="B7" t="n">
-        <v>93235</v>
+        <v>93345</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1226,34 +1244,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Västerbottens län, Vb</t>
+          <t>Nördrengårdsmyran, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>785964</v>
+        <v>785985</v>
       </c>
       <c r="R7" t="n">
-        <v>7216907</v>
+        <v>7216828</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1280,17 +1298,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-09-06</t>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-09-06</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Sweco NVI</t>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1305,49 +1328,53 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Tobias Pettersson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Tobias Pettersson</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/113441439</t>
+          <t>https://artportalen.se/Sighting/134650458</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113441460</v>
+        <v>113441419</v>
       </c>
       <c r="B8" t="n">
-        <v>79327</v>
+        <v>93209</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>4366</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1357,10 +1384,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>786139</v>
+        <v>785912</v>
       </c>
       <c r="R8" t="n">
-        <v>7217057</v>
+        <v>7216875</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1423,38 +1450,38 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/113441460</t>
+          <t>https://artportalen.se/Sighting/113441419</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113441461</v>
+        <v>113441438</v>
       </c>
       <c r="B9" t="n">
-        <v>79327</v>
+        <v>93235</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>5966</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1464,10 +1491,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>786080</v>
+        <v>786219</v>
       </c>
       <c r="R9" t="n">
-        <v>7216837</v>
+        <v>7217228</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1530,16 +1557,16 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/113441461</t>
+          <t>https://artportalen.se/Sighting/113441438</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113441448</v>
+        <v>113441439</v>
       </c>
       <c r="B10" t="n">
-        <v>79084</v>
+        <v>93235</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1547,21 +1574,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6446</v>
+        <v>5966</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1571,10 +1598,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>785935</v>
+        <v>785964</v>
       </c>
       <c r="R10" t="n">
-        <v>7216929</v>
+        <v>7216907</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1637,7 +1664,818 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/113441439</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>113441460</v>
+      </c>
+      <c r="B11" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Västerbottens län, Vb</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>786139</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7217057</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Byske</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2023-09-06</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2023-09-06</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Sweco NVI</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Tobias Pettersson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Tobias Pettersson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113441460</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>113441461</v>
+      </c>
+      <c r="B12" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Västerbottens län, Vb</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>786080</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7216837</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Byske</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2023-09-06</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2023-09-06</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Sweco NVI</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Tobias Pettersson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Tobias Pettersson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113441461</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>134650489</v>
+      </c>
+      <c r="B13" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Nördrengårdsmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>786100</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7217086</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Byske</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>12:58</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>12:58</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134650489</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>113441448</v>
+      </c>
+      <c r="B14" t="n">
+        <v>79084</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Västerbottens län, Vb</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>785935</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7216929</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Byske</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2023-09-06</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2023-09-06</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Sweco NVI</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Tobias Pettersson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Tobias Pettersson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/113441448</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>134650462</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Nördrengårdsmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>786092</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7216833</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Byske</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>11:52</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>11:52</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Barksprätt</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134650462</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>134650464</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Nördrengårdsmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>786099</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7216832</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Byske</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Färska barksprätt bild</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134650464</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>134650460</v>
+      </c>
+      <c r="B17" t="n">
+        <v>99296</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Nördrengårdsmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>786013</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7216864</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Byske</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134650460</t>
         </is>
       </c>
     </row>
@@ -1652,6 +2490,13 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 26645-2026 artfynd.xlsx
+++ b/artfynd/A 26645-2026 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>134650454</v>
       </c>
       <c r="B3" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>134650456</v>
       </c>
       <c r="B4" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1236,7 +1236,7 @@
         <v>134650458</v>
       </c>
       <c r="B7" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
         <v>134650460</v>
       </c>
       <c r="B17" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 26645-2026 artfynd.xlsx
+++ b/artfynd/A 26645-2026 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>134650454</v>
       </c>
       <c r="B3" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>134650456</v>
       </c>
       <c r="B4" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1236,7 +1236,7 @@
         <v>134650458</v>
       </c>
       <c r="B7" t="n">
-        <v>93347</v>
+        <v>93362</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1887,7 +1887,7 @@
         <v>134650489</v>
       </c>
       <c r="B13" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2110,7 +2110,7 @@
         <v>134650462</v>
       </c>
       <c r="B15" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2239,7 +2239,7 @@
         <v>134650464</v>
       </c>
       <c r="B16" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
         <v>134650460</v>
       </c>
       <c r="B17" t="n">
-        <v>99298</v>
+        <v>99315</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 26645-2026 artfynd.xlsx
+++ b/artfynd/A 26645-2026 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>134650454</v>
       </c>
       <c r="B3" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>134650456</v>
       </c>
       <c r="B4" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1236,7 +1236,7 @@
         <v>134650458</v>
       </c>
       <c r="B7" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1887,7 +1887,7 @@
         <v>134650489</v>
       </c>
       <c r="B13" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
         <v>134650460</v>
       </c>
       <c r="B17" t="n">
-        <v>99315</v>
+        <v>99316</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 26645-2026 artfynd.xlsx
+++ b/artfynd/A 26645-2026 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>134650454</v>
       </c>
       <c r="B3" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>134650456</v>
       </c>
       <c r="B4" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1236,7 +1236,7 @@
         <v>134650458</v>
       </c>
       <c r="B7" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
         <v>134650460</v>
       </c>
       <c r="B17" t="n">
-        <v>99316</v>
+        <v>99317</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 26645-2026 artfynd.xlsx
+++ b/artfynd/A 26645-2026 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>134650454</v>
       </c>
       <c r="B3" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>134650456</v>
       </c>
       <c r="B4" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1236,7 +1236,7 @@
         <v>134650458</v>
       </c>
       <c r="B7" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1887,7 +1887,7 @@
         <v>134650489</v>
       </c>
       <c r="B13" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2110,7 +2110,7 @@
         <v>134650462</v>
       </c>
       <c r="B15" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2239,7 +2239,7 @@
         <v>134650464</v>
       </c>
       <c r="B16" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
         <v>134650460</v>
       </c>
       <c r="B17" t="n">
-        <v>99317</v>
+        <v>99318</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 26645-2026 artfynd.xlsx
+++ b/artfynd/A 26645-2026 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>134650454</v>
       </c>
       <c r="B3" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>134650456</v>
       </c>
       <c r="B4" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1236,7 +1236,7 @@
         <v>134650458</v>
       </c>
       <c r="B7" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1887,7 +1887,7 @@
         <v>134650489</v>
       </c>
       <c r="B13" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2110,7 +2110,7 @@
         <v>134650462</v>
       </c>
       <c r="B15" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2239,7 +2239,7 @@
         <v>134650464</v>
       </c>
       <c r="B16" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
         <v>134650460</v>
       </c>
       <c r="B17" t="n">
-        <v>99318</v>
+        <v>99324</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 26645-2026 artfynd.xlsx
+++ b/artfynd/A 26645-2026 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>134650454</v>
       </c>
       <c r="B3" t="n">
-        <v>92073</v>
+        <v>92074</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>134650456</v>
       </c>
       <c r="B4" t="n">
-        <v>92073</v>
+        <v>92074</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1236,7 +1236,7 @@
         <v>134650458</v>
       </c>
       <c r="B7" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1887,7 +1887,7 @@
         <v>134650489</v>
       </c>
       <c r="B13" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2110,7 +2110,7 @@
         <v>134650462</v>
       </c>
       <c r="B15" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2239,7 +2239,7 @@
         <v>134650464</v>
       </c>
       <c r="B16" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
         <v>134650460</v>
       </c>
       <c r="B17" t="n">
-        <v>99324</v>
+        <v>99325</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 26645-2026 artfynd.xlsx
+++ b/artfynd/A 26645-2026 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>134650454</v>
       </c>
       <c r="B3" t="n">
-        <v>92074</v>
+        <v>92080</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>134650456</v>
       </c>
       <c r="B4" t="n">
-        <v>92074</v>
+        <v>92080</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1236,7 +1236,7 @@
         <v>134650458</v>
       </c>
       <c r="B7" t="n">
-        <v>93372</v>
+        <v>93378</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1887,7 +1887,7 @@
         <v>134650489</v>
       </c>
       <c r="B13" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
         <v>134650460</v>
       </c>
       <c r="B17" t="n">
-        <v>99325</v>
+        <v>99336</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 26645-2026 artfynd.xlsx
+++ b/artfynd/A 26645-2026 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>134650454</v>
       </c>
       <c r="B3" t="n">
-        <v>92080</v>
+        <v>92087</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>134650456</v>
       </c>
       <c r="B4" t="n">
-        <v>92080</v>
+        <v>92087</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1236,7 +1236,7 @@
         <v>134650458</v>
       </c>
       <c r="B7" t="n">
-        <v>93378</v>
+        <v>93385</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1887,7 +1887,7 @@
         <v>134650489</v>
       </c>
       <c r="B13" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2110,7 +2110,7 @@
         <v>134650462</v>
       </c>
       <c r="B15" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2239,7 +2239,7 @@
         <v>134650464</v>
       </c>
       <c r="B16" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
         <v>134650460</v>
       </c>
       <c r="B17" t="n">
-        <v>99336</v>
+        <v>99349</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 26645-2026 artfynd.xlsx
+++ b/artfynd/A 26645-2026 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>134650454</v>
       </c>
       <c r="B3" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>134650456</v>
       </c>
       <c r="B4" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1236,7 +1236,7 @@
         <v>134650458</v>
       </c>
       <c r="B7" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
         <v>134650460</v>
       </c>
       <c r="B17" t="n">
-        <v>99349</v>
+        <v>99350</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
